--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/02. Trả bảo hành/TBH_ThanhTamNhaTrang_200326.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/02. Trả bảo hành/TBH_ThanhTamNhaTrang_200326.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 03\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52DC2AE-5A9E-4CA7-9EFC-CF03FB3E914D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P.TraBaoHanh" sheetId="1" r:id="rId1"/>
@@ -165,7 +166,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
@@ -450,7 +451,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -542,20 +543,41 @@
     <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -589,30 +611,6 @@
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -688,9 +686,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -728,9 +726,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -765,7 +763,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -800,7 +798,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -973,7 +971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J66"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -992,77 +990,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="43" t="s">
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="44" t="s">
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="46"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="47" t="s">
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="49"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="50" t="s">
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="52"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="25"/>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
@@ -1070,12 +1068,12 @@
       <c r="I6" s="33"/>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
       <c r="E7" s="25"/>
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
@@ -1083,12 +1081,12 @@
       <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
       <c r="E8" s="25"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
@@ -1096,12 +1094,12 @@
       <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="56"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
       <c r="E9" s="25"/>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
@@ -1149,14 +1147,14 @@
         <v>44</v>
       </c>
       <c r="D11" s="36"/>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41" t="s">
+      <c r="F11" s="40"/>
+      <c r="G11" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="40" t="s">
         <v>45</v>
       </c>
       <c r="I11" s="36"/>
@@ -1173,16 +1171,16 @@
         <v>30</v>
       </c>
       <c r="D12" s="36"/>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="40" t="s">
         <v>37</v>
       </c>
       <c r="I12" s="36"/>
@@ -1201,14 +1199,14 @@
       <c r="D13" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="40" t="s">
         <v>27</v>
       </c>
       <c r="F13" s="34"/>
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="40" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="36"/>
@@ -1225,43 +1223,43 @@
         <v>32</v>
       </c>
       <c r="D14" s="36"/>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="40" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="36"/>
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="40"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="39"/>
       <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="39"/>
       <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1271,41 +1269,41 @@
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="38" t="s">
+      <c r="G17" s="8"/>
+      <c r="H17" s="37" t="s">
         <v>43</v>
       </c>
       <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="59"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
       <c r="E18" s="15"/>
       <c r="F18" s="13"/>
-      <c r="G18" s="57" t="s">
+      <c r="G18" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
     </row>
     <row r="19" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="58" t="s">
+      <c r="A19" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
       <c r="E19" s="27"/>
       <c r="F19" s="26"/>
-      <c r="G19" s="58" t="s">
+      <c r="G19" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
     </row>
     <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="30"/>
@@ -1352,19 +1350,19 @@
       <c r="I23" s="17"/>
     </row>
     <row r="24" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="59" t="s">
+      <c r="A24" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
       <c r="E24" s="15"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="59" t="s">
+      <c r="G24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
     </row>
     <row r="25" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
@@ -1378,12 +1376,17 @@
       <c r="I25" s="19"/>
     </row>
     <row r="27" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B27" s="55"/>
-      <c r="C27" s="55"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
     </row>
     <row r="66" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A6:D6"/>
@@ -1397,11 +1400,6 @@
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.78740157480314965" top="0.98425196850393704" bottom="0.98425196850393704" header="0" footer="0"/>
